--- a/Modulo4/aula335, 336 e 337/workbook2.xlsx
+++ b/Modulo4/aula335, 336 e 337/workbook2.xlsx
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>9.699999999999999</v>
